--- a/output/pdf_financials_xlsx/CEC.xlsx
+++ b/output/pdf_financials_xlsx/CEC.xlsx
@@ -3919,16 +3919,16 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.032</v>
       </c>
     </row>
     <row r="125">
@@ -3948,16 +3948,16 @@
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.032</v>
       </c>
     </row>
     <row r="126">
@@ -6386,7 +6386,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
